--- a/LoanOfficer-A/2023/81 asiqi.xlsx
+++ b/LoanOfficer-A/2023/81 asiqi.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>6000</v>
+        <v>7500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>54000</v>
+        <v>52500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1240,9 +1240,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45627</v>
+      </c>
+      <c r="C15" s="4">
+        <v>500</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1266,9 +1272,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45628</v>
+      </c>
+      <c r="C16" s="4">
+        <v>500</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1292,9 +1304,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45628</v>
+      </c>
+      <c r="C17" s="4">
+        <v>500</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>

--- a/LoanOfficer-A/2023/81 asiqi.xlsx
+++ b/LoanOfficer-A/2023/81 asiqi.xlsx
@@ -602,7 +602,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -804,7 +804,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>52500</v>
+        <v>50000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1336,9 +1336,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C18" s="4">
+        <v>500</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1362,9 +1368,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C19" s="4">
+        <v>500</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1388,9 +1400,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C20" s="4">
+        <v>500</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1414,9 +1432,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C21" s="4">
+        <v>500</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1440,9 +1464,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45632</v>
+      </c>
+      <c r="C22" s="4">
+        <v>500</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
